--- a/profiles.xlsx
+++ b/profiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,6 +1502,171 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PV171122MWEI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Praneeth</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>veleti</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3y 3m 16d 17:40:52</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>lkg</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SK050321FMMP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Samhita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kandula</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5y 0m 0d 17:47:17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Mother mary</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Parasigutta</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lkg</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>veleti</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4y 7m 9d 17:54:49</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>abids</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ukg</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/profiles.xlsx
+++ b/profiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,112 +476,7457 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PM181122FDOH</t>
+          <t>AK140920MATN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pallavi</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>manetha</t>
-        </is>
-      </c>
+          <t>Ankith</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3y 3m 27d 19:37:56</t>
+          <t>5 years 5 months 27 days</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>donbosco</t>
+          <t>AMARAVATHI TALENT SCHOOL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>hydershakote</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>LKG</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PR150722MDOH</t>
+          <t>MP100821FVVS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Praneeth</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>reddy</t>
-        </is>
-      </c>
+          <t>MedhaSree</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4 years 6 months 27 days</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SS121120FVVS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHANMUKHA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2020-11-12</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5 years 3 months 25 days</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HUGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SM130122FVVS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SATHWIKA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2022-01-13</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4 years 1 months 24 days</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RM290322FVVS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rajasvi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3y 8m 2d 19:43:47</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>donbosco</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>hydershakote</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>LKG</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3 years 11 months 8 days</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JD310521MVVS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JASHWANTH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4 years 9 months 6 days</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PS060722FVVS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pujya Shree</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3 years 8 months 3 days</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AM230123FVVS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ANJANA DEVI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3 years 1 months 14 days</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GM160722MVVS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ganadeep</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3 years 7 months 21 days</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PJ290822MVVS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Puneet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3 years 6 months 8 days</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RM220222FVVS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rohshikaa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2022-02-22</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4 years 0 months 15 days</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SM210820MVVS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHIVANSH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2020-08-21</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5 years 6 months 16 days</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VM170921MVVS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VIRAAJ JAI NANDA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4 years 5 months 20 days</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AP050222MVVS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Adwith Yadav</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4 years 1 months 4 days</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HT040921MVVS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hanshith</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2021-09-04</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4 years 6 months 5 days</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RK181020MVVS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rohit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2020-10-18</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5 years 4 months 19 days</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>YM280122MVVS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yokshith Vagdev</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4 years 1 months 9 days</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GV060620MVVS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GAGAN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2020-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5 years 9 months 3 days</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ST080721MVVS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sushanth</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4 years 8 months 1 days</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DB020322FVVS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DAKSHA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2022-03-02</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4 years 0 months 7 days</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NM170122FVVS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nikshitha</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2022-01-17</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4 years 1 months 20 days</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JR071221FVVS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jeshmitha</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2021-12-07</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4 years 3 months 2 days</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CU020721FVVS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CHAITRA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4 years 8 months 7 days</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SA030621FVVS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sohitha</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4 years 9 months 6 days</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RA150822MVVS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rudra Dev</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3 years 6 months 22 days</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AP020121MVVS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ABHINEETH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2021-01-02</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5 years 2 months 7 days</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GJ151221MVVS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gaurav</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4 years 2 months 22 days</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LB230420FVVS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LIPIKA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2020-04-23</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5 years 10 months 14 days</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HJ251121MVVS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Harsh</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4 years 3 months 12 days</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MM200421FVVS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4 years 10 months 17 days</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SP081020MVVS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SHREEDHAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2020-10-08</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5 years 5 months 1 days</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RB020221FVVS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rishwitha</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2021-02-02</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5 years 1 months 7 days</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LS080920MVVS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LOKESH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2020-09-08</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5 years 6 months 1 days</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DA291020MVVS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2020-10-29</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5 years 4 months 8 days</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MA291020MVVS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Manu</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2020-10-29</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5 years 4 months 8 days</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BS190121MVVS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BALA DEVIKNANDHAN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2021-01-19</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5 years 1 months 18 days</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SS070122FVVS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Srinika</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2022-01-07</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4 years 2 months 2 days</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MM210921MVVS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MANIKANTA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4 years 5 months 16 days</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SS130221MVVS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sahans</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2021-02-13</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5 years 0 months 24 days</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ST100920FVVS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shree Renuka</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5 years 5 months 27 days</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SP231221MVVS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SHIVANSH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2021-12-23</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4 years 2 months 14 days</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>YT251122FVVS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Yeshwika</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2022-11-25</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3 years 3 months 12 days</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SR101220MVVS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Shanmukha Chary</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5 years 2 months 27 days</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RM030521FVVS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rutvik</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4 years 10 months 6 days</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vedic vidyalam</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>YH030720MVVS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Yugan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5 years 8 months 6 days</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vedic vidyalam</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SB060122MVVS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SATHWIK NAYAK</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2022-01-06</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4 years 2 months 3 days</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MT300722FVVS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mahira</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2022-07-30</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3 years 7 months 7 days</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NP071021MVVS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nihal</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4 years 5 months 2 days</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vedic vidyalam</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AT300422FVVS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Aayra</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3 years 10 months 7 days</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AK250620FVVS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ALIYA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>5 years 8 months 12 days</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MV211220FVVS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Madhava priya</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2020-12-21</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5 years 2 months 16 days</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Vedic vidyalam</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EB191121MVVS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Eeshan Karthik</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2021-11-19</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4 years 3 months 18 days</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HK070821MVVS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Harshavardhan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4 years 7 months 2 days</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VT090920FVVS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VAAGMI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5 years 6 months 0 days</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>HS090821FVVS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Harshitha</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4 years 7 months 0 days</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SP211220FVVS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Samiksha</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2020-12-21</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5 years 2 months 16 days</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KP210520FVVS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KARTHIKA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2020-05-21</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>5 years 9 months 16 days</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SK270520FVVS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Siri Vennala</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5 years 9 months 10 days</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SD290920FVVS</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Saanvi</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2020-09-29</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>5 years 5 months 8 days</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MM160920MVVS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Manvith</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>5 years 5 months 21 days</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MG250722MVVS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mahan Yadav</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3 years 7 months 12 days</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GG120920MVVS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gynanshwar</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2020-09-12</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5 years 5 months 25 days</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Vedic vidyayalam</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VD121020MVVS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>VRISHANK</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2020-10-12</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5 years 4 months 25 days</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AM240222MVVS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Advik Nandhan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4 years 0 months 13 days</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RB170422MVVS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RUDRANSH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2022-04-17</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3 years 10 months 20 days</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FM160721MVVS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Faizaan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>4 years 7 months 21 days</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>YG021022MVVS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Yashwanth</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3 years 5 months 7 days</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>JG040122FVVS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Janvika</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>4 years 2 months 5 days</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SK061120FVVS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SNEHA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5 years 4 months 3 days</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DN191120MVVS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dakshith</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2020-11-19</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>5 years 3 months 18 days</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AP210720MVVS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Abhinav</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>5 years 7 months 16 days</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KG201021FVVS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jabbar</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>4 years 3 months 4 days</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JM051221MVVS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Jabbar</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>4 years 3 months 4 days</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>NM150821FVVS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nitya Sree</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>4 years 6 months 22 days</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SV190920MVVS</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Samantha Rana</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>5 years 5 months 18 days</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SA030322MVVS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Shiv Adithya</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4 years 0 months 6 days</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GB060121FVVS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ganavika</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2021-01-06</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>5 years 2 months 3 days</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JN141021MVVS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jatin</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>4 years 4 months 23 days</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VT100821MVVS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>4 years 6 months 27 days</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BR241020FVVS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bala bramarambha</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>5 years 4 months 13 days</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>JM170420MVVS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Junaid Ahmed</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2020-04-17</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>5 years 10 months 20 days</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SG030221FVVS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Srinidhi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2021-02-03</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>5 years 1 months 6 days</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AT121222FVVS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Aadhya Sri</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>3 years 2 months 25 days</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AS070620MVVS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>5 years 9 months 2 days</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ST111220FSSN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Shaarvi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2020-12-11</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>5 years 3 months 1 days</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CC100122MSSN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Charan</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>4 years 2 months 2 days</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VB070421FSSN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Vedanshi</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2021-04-07</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>4 years 11 months 5 days</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SK081220MSSN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sri Teja</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2020-12-08</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>5 years 3 months 4 days</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>YB260820MSSN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Yashwin</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>5 years 6 months 14 days</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ST270420FSSN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sri Latha</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>5 years 10 months 13 days</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>LK220722MSSN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Lokesh Bharadwaj</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2022-07-22</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>3 years 7 months 18 days</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BB120121MSSN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Baviyan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>5 years 2 months 0 days</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SM201020MSSN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sree Ram</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>5 years 4 months 20 days</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AN020321FSSN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Abeeha</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>5 years 0 months 10 days</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VV100621MSSN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Vignesh</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>4 years 9 months 2 days</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HG200920FSSN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Haasini</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2020-09-20</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>5 years 5 months 20 days</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AB111021MSSN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Akhil Nayak</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>4 years 5 months 1 days</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AB220920FSSN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Aparna</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>5 years 5 months 18 days</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>JB090620MSSN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jeevan</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2020-06-09</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>5 years 9 months 3 days</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sree Saraswathi School</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>RR160921FSSN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Rishika</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>4 years 5 months 24 days</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SK230920MSSN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Shrinay</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>5 years 5 months 17 days</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>KR150621FSSN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kruthika</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>4 years 8 months 25 days</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SS300521MSSN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sushanth</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2021-05-30</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4 years 9 months 10 days</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PG191122MSSN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pratyush</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2022-11-19</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>3 years 3 months 21 days</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KG150820MSSN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kalyan Kumar</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>5 years 6 months 25 days</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SN261022FSSN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sanvika</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3 years 4 months 14 days</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LS140922MSSN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Likith Ganesh</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>3 years 5 months 26 days</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AG020422FSSN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Anvika</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>3 years 11 months 10 days</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SK280721FSSN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sudhakar</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>4 years 7 months 12 days</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MN210222MSSN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Mallikarjun</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2022-02-21</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>4 years 0 months 19 days</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DJ180321MSSN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Dheeraj Nandan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>4 years 11 months 22 days</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KS190123FSSN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Kruthi</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>3 years 1 months 21 days</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NK290421MSSN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nihanth</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>4 years 10 months 11 days</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sree Saraswathi school</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>RK300620FSSN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rishika</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>5 years 8 months 10 days</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>HK170820FSSN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hiranmai</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>5 years 6 months 23 days</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Shridi Sai Baba School</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SG071121FATN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Sejal</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2021-11-07</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>4 years 4 months 6 days</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SK300322MATN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ankith</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>5 years 5 months 27 days</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AK141221MATN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Afan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2021-12-14</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>4 years 2 months 27 days</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VJ031220MATN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vedh</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2020-12-03</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>5 years 3 months 10 days</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>VR011220FATN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Vilina</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>5 years 3 months 12 days</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AB160621MATN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sejal</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2021-11-07</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>4 years 4 months 6 days</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VG290621MATN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Vedh</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2020-12-03</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>5 years 3 months 10 days</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>YJ270920MATN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AA060921FATN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Afan</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2021-12-14</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>4 years 2 months 27 days</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>HS110822MATN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Hrudayansh</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3 years 7 months 2 days</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AJ310721MATN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Aarush</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>4 years 7 months 10 days</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DV250522FATN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Darshana</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>3 years 9 months 16 days</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HB061020FATN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Haniya</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>5 years 5 months 7 days</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HM061020MATN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>5 years 5 months 7 days</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>OG041120MATN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Oansh</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>5 years 4 months 9 days</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SP091121FATN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Srehitha</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>4 years 4 months 4 days</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AA010821FATN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ananya</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>4 years 7 months 12 days</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MG111121MATN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mustafa</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>4</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>4 years 4 months 2 days</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VS160922FATN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Vrishrudha</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3 years 5 months 25 days</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>JD021020MATN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Jagan Mohan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>5</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>5 years 5 months 11 days</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PP040520MATN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Hemansh</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>3</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>3 years 7 months 2 days</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VV201121MATN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Vedhansh</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2021-11-20</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>4 years 3 months 21 days</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HG110822MATN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Hemansh</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>3 years 7 months 2 days</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MB300422MATN</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Manvith</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>3 years 10 months 11 days</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>AMARAVATHI TALENT SCHOOL</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MM230421FAGM</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Madhupriya Sree</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2021-04-23</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>4 years 10 months 19 days</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>LB110521FAGM</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lishvitha</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>4 years 10 months 3 days</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>NC060221FAGM</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Niharitha</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2021-02-06</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>5 years 1 months 8 days</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>VM210421FAGM</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Vithika</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>4 years 10 months 21 days</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>LV240622MAGM</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Lakshith</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>3 years 8 months 18 days</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>KB240221FAGM</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Kriti</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>5 years 0 months 18 days</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CP260821FAGM</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Chaitanya</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2021-08-26</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>4</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>4 years 6 months 16 days</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SK101221MAGM</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Srihan Krishna</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2021-12-10</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>4</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>4 years 3 months 4 days</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DR121221FAGM</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Dhanvi</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2021-12-12</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>4 years 3 months 2 days</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>LL100521FAGM</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Loksha</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>4 years 10 months 4 days</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DB261121MAGM</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Darshal</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>4 years 3 months 16 days</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TK250121FAGM</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Teja Sree</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2021-01-25</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>5</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>5 years 1 months 17 days</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SK161121MAGM</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Shivansh Karthikeya</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>4</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>4 years 3 months 26 days</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CU201221FAGM</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Chaitanya Charan</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2021-12-20</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>4</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>4 years 2 months 22 days</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>LS270821FAGM</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lavanya</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>4 years 6 months 15 days</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>LT181122FAGM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Loukya Sri</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>3 years 3 months 24 days</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AG070722FAGM</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ankitha</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>3 years 8 months 7 days</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>VG240421FAGM</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Vedhika</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>4</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>4 years 10 months 18 days</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Amaravathi Grammar High School</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RR160322MWHT</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2022-03-16</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>4</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>4 years 0 months 0 days</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Westside high</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>RM031220FSST</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ruchira</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2020-12-03</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>5</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>5 years 3 months 14 days</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>UM260622MSST</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Unith</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>3</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>3 years 8 months 19 days</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SM090622MSST</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Srihansh</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>3</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>3 years 9 months 8 days</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AM230520MSST</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Arfaza</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2020-05-23</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>5</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>5 years 9 months 22 days</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>NS060321MSST</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nithin</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>5</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>5 years 0 months 11 days</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>YL060620FSST</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Yogitha</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2020-06-06</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>5</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>5 years 9 months 11 days</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>RJ190920MSST</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Reiaan</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>5</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>5 years 5 months 26 days</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SB090921MSST</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Srimanth</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>4 years 6 months 8 days</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>LG181121MSST</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Lithvik</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>4 years 3 months 27 days</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SC010121MSST</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Shrehas</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>5 years 2 months 16 days</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SL131020FSST</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sahiti</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>5</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>5 years 5 months 4 days</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SK270820MSST</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sheshank</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>5</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>5 years 6 months 18 days</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SK190522FSST</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Sahasra</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>3</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>3 years 9 months 26 days</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>NI171221MSST</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Nikhil Nayak</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2021-12-17</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>4</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>4 years 3 months 0 days</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sri Sai Vidyarthi High School</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>BK120121MATN</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Baladithya</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CC100122MSSA</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Charan</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>VG120920FSSN</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Vijaya</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2020-09-12</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profiles.xlsx
+++ b/profiles.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profiles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,8 +490,10 @@
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -533,8 +535,10 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>4</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -576,8 +580,10 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -619,8 +625,10 @@
           <t>2022-01-13</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -662,8 +670,10 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -705,8 +715,10 @@
           <t>2021-05-31</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -748,8 +760,10 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -791,8 +805,10 @@
           <t>2023-01-23</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -834,8 +850,10 @@
           <t>2022-07-16</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>3</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -877,8 +895,10 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -920,8 +940,10 @@
           <t>2022-02-22</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -963,8 +985,10 @@
           <t>2020-08-21</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>5</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1006,8 +1030,10 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>4</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1049,8 +1075,10 @@
           <t>2022-02-05</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>4</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1092,8 +1120,10 @@
           <t>2021-09-04</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>4</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1135,8 +1165,10 @@
           <t>2020-10-18</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>5</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1178,8 +1210,10 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>4</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1221,8 +1255,10 @@
           <t>2020-06-06</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>5</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1264,8 +1300,10 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>4</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1307,8 +1345,10 @@
           <t>2022-03-02</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>4</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1350,8 +1390,10 @@
           <t>2022-01-17</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>4</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1393,8 +1435,10 @@
           <t>2021-12-07</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>4</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,8 +1480,10 @@
           <t>2021-07-02</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>4</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1479,8 +1525,10 @@
           <t>2021-06-03</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>4</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1522,8 +1570,10 @@
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>3</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1565,8 +1615,10 @@
           <t>2021-01-02</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>5</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1608,8 +1660,10 @@
           <t>2021-12-15</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>4</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1651,8 +1705,10 @@
           <t>2020-04-23</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>5</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1694,8 +1750,10 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>4</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1737,8 +1795,10 @@
           <t>2021-04-20</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>4</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1780,8 +1840,10 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>5</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1823,8 +1885,10 @@
           <t>2021-02-02</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>5</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1866,8 +1930,10 @@
           <t>2020-09-08</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>5</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1909,8 +1975,10 @@
           <t>2020-10-29</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>5</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1952,8 +2020,10 @@
           <t>2020-10-29</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>5</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1995,8 +2065,10 @@
           <t>2021-01-19</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>5</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2038,8 +2110,10 @@
           <t>2022-01-07</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>4</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2081,8 +2155,10 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>4</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2124,8 +2200,10 @@
           <t>2021-02-13</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>5</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2167,8 +2245,10 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>5</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2210,8 +2290,10 @@
           <t>2021-12-23</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>4</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2253,8 +2335,10 @@
           <t>2022-11-25</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>3</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2296,8 +2380,10 @@
           <t>2020-12-10</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>5</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2339,8 +2425,10 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>4</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2382,8 +2470,10 @@
           <t>2020-07-03</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>5</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2425,8 +2515,10 @@
           <t>2022-01-06</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>4</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2468,8 +2560,10 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>3</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2511,8 +2605,10 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>4</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2550,8 +2646,10 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>3</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2593,8 +2691,10 @@
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>5</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2636,8 +2736,10 @@
           <t>2020-12-21</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>5</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2679,8 +2781,10 @@
           <t>2021-11-19</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>4</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2722,8 +2826,10 @@
           <t>2021-08-07</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>4</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2765,8 +2871,10 @@
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>5</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2808,8 +2916,10 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>4</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2851,8 +2961,10 @@
           <t>2020-12-21</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>5</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2894,8 +3006,10 @@
           <t>2020-05-21</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>5</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2937,8 +3051,10 @@
           <t>2020-05-27</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>5</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2980,8 +3096,10 @@
           <t>2020-09-29</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>5</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3023,8 +3141,10 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>5</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3066,8 +3186,10 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>3</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3109,8 +3231,10 @@
           <t>2020-09-12</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>5</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3152,8 +3276,10 @@
           <t>2020-10-12</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>5</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3195,8 +3321,10 @@
           <t>2022-02-24</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>4</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3238,8 +3366,10 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>3</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3281,8 +3411,10 @@
           <t>2021-07-16</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>4</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3324,8 +3456,10 @@
           <t>2022-10-02</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>3</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3367,8 +3501,10 @@
           <t>2022-01-04</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>4</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3410,8 +3546,10 @@
           <t>2020-11-06</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>5</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3453,8 +3591,10 @@
           <t>2020-11-19</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>5</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3496,8 +3636,10 @@
           <t>2020-07-21</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>5</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3539,8 +3681,10 @@
           <t>2021-12-05</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>4</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3582,8 +3726,10 @@
           <t>2021-12-05</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>4</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3625,8 +3771,10 @@
           <t>2021-08-15</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>4</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3668,8 +3816,10 @@
           <t>2020-09-19</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>5</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3711,8 +3861,10 @@
           <t>2022-03-03</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>4</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3754,8 +3906,10 @@
           <t>2021-01-06</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>5</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3797,8 +3951,10 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>4</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3840,8 +3996,10 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>4</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3879,8 +4037,10 @@
           <t>2020-10-24</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>5</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3922,8 +4082,10 @@
           <t>2020-04-17</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>5</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3965,8 +4127,10 @@
           <t>2021-02-03</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>5</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4008,8 +4172,10 @@
           <t>2022-12-12</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>3</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4051,8 +4217,10 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>5</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4094,8 +4262,10 @@
           <t>2020-12-11</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>5</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4137,8 +4307,10 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>4</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4180,8 +4352,10 @@
           <t>2021-04-07</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>4</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4223,8 +4397,10 @@
           <t>2020-12-08</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>5</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4266,8 +4442,10 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>5</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4309,8 +4487,10 @@
           <t>2020-04-27</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>5</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4352,8 +4532,10 @@
           <t>2022-07-22</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>3</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4395,8 +4577,10 @@
           <t>2021-01-12</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>5</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4438,8 +4622,10 @@
           <t>2020-10-20</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>5</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4481,8 +4667,10 @@
           <t>2021-03-02</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>5</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4524,8 +4712,10 @@
           <t>2021-06-10</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>4</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4567,8 +4757,10 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>5</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4610,8 +4802,10 @@
           <t>2021-10-11</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>4</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4653,8 +4847,10 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>5</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4696,8 +4892,10 @@
           <t>2020-06-09</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>5</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4739,8 +4937,10 @@
           <t>2021-09-16</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>4</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4782,8 +4982,10 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>5</v>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4825,8 +5027,10 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>4</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4868,8 +5072,10 @@
           <t>2021-05-30</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v>4</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4911,8 +5117,10 @@
           <t>2022-11-19</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>3</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4954,8 +5162,10 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>5</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4997,8 +5207,10 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>3</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5040,8 +5252,10 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>3</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5083,8 +5297,10 @@
           <t>2022-04-02</t>
         </is>
       </c>
-      <c r="E109" t="n">
-        <v>3</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5126,8 +5342,10 @@
           <t>2021-07-28</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v>4</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5169,8 +5387,10 @@
           <t>2022-02-21</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v>4</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5212,8 +5432,10 @@
           <t>2021-03-18</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>4</v>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5255,8 +5477,10 @@
           <t>2023-01-19</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>3</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5298,8 +5522,10 @@
           <t>2021-04-29</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>4</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5341,8 +5567,10 @@
           <t>2020-06-30</t>
         </is>
       </c>
-      <c r="E115" t="n">
-        <v>5</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5384,8 +5612,10 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v>5</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5427,8 +5657,10 @@
           <t>2021-11-07</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>4</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5470,8 +5702,10 @@
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="E118" t="n">
-        <v>5</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5513,8 +5747,10 @@
           <t>2021-12-14</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>4</v>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5556,8 +5792,10 @@
           <t>2020-12-03</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>5</v>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5595,8 +5833,10 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v>5</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5638,8 +5878,10 @@
           <t>2021-11-07</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>4</v>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5681,8 +5923,10 @@
           <t>2020-12-03</t>
         </is>
       </c>
-      <c r="E123" t="n">
-        <v>5</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5716,8 +5960,10 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="E124" t="n">
-        <v>3</v>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
@@ -5747,8 +5993,10 @@
           <t>2021-12-14</t>
         </is>
       </c>
-      <c r="E125" t="n">
-        <v>4</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5790,8 +6038,10 @@
           <t>2022-08-11</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v>3</v>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5833,8 +6083,10 @@
           <t>2021-07-31</t>
         </is>
       </c>
-      <c r="E127" t="n">
-        <v>4</v>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5876,8 +6128,10 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>3</v>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5919,8 +6173,10 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="E129" t="n">
-        <v>5</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5962,8 +6218,10 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>5</v>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6005,8 +6263,10 @@
           <t>2020-11-04</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>5</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6048,8 +6308,10 @@
           <t>2021-11-09</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>4</v>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6091,8 +6353,10 @@
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="E133" t="n">
-        <v>4</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6134,8 +6398,10 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v>4</v>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6177,8 +6443,10 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="E135" t="n">
-        <v>3</v>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6220,8 +6488,10 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="E136" t="n">
-        <v>5</v>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6263,8 +6533,10 @@
           <t>2022-08-11</t>
         </is>
       </c>
-      <c r="E137" t="n">
-        <v>3</v>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6306,8 +6578,10 @@
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="E138" t="n">
-        <v>4</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6349,8 +6623,10 @@
           <t>2022-08-11</t>
         </is>
       </c>
-      <c r="E139" t="n">
-        <v>3</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6392,8 +6668,10 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="E140" t="n">
-        <v>3</v>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6431,8 +6709,10 @@
           <t>2021-04-23</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>4</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6474,8 +6754,10 @@
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>4</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6517,8 +6799,10 @@
           <t>2021-02-06</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>5</v>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6560,8 +6844,10 @@
           <t>2021-04-21</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>4</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6603,8 +6889,10 @@
           <t>2022-06-24</t>
         </is>
       </c>
-      <c r="E145" t="n">
-        <v>3</v>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6646,8 +6934,10 @@
           <t>2021-02-24</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v>5</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6689,8 +6979,10 @@
           <t>2021-08-26</t>
         </is>
       </c>
-      <c r="E147" t="n">
-        <v>4</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6732,8 +7024,10 @@
           <t>2021-12-10</t>
         </is>
       </c>
-      <c r="E148" t="n">
-        <v>4</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6775,8 +7069,10 @@
           <t>2021-12-12</t>
         </is>
       </c>
-      <c r="E149" t="n">
-        <v>4</v>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6818,8 +7114,10 @@
           <t>2021-05-10</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v>4</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6861,8 +7159,10 @@
           <t>2021-11-26</t>
         </is>
       </c>
-      <c r="E151" t="n">
-        <v>4</v>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -6904,8 +7204,10 @@
           <t>2021-01-25</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v>5</v>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -6947,8 +7249,10 @@
           <t>2021-11-16</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v>4</v>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -6990,8 +7294,10 @@
           <t>2021-12-20</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v>4</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7033,8 +7339,10 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>4</v>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7076,8 +7384,10 @@
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>3</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7119,8 +7429,10 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="E157" t="n">
-        <v>3</v>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7162,8 +7474,10 @@
           <t>2021-04-24</t>
         </is>
       </c>
-      <c r="E158" t="n">
-        <v>4</v>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7205,8 +7519,10 @@
           <t>2022-03-16</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v>4</v>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7244,8 +7560,10 @@
           <t>2020-12-03</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v>5</v>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7287,8 +7605,10 @@
           <t>2022-06-26</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v>3</v>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -7330,8 +7650,10 @@
           <t>2022-06-09</t>
         </is>
       </c>
-      <c r="E162" t="n">
-        <v>3</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7373,8 +7695,10 @@
           <t>2020-05-23</t>
         </is>
       </c>
-      <c r="E163" t="n">
-        <v>5</v>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7416,8 +7740,10 @@
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="E164" t="n">
-        <v>5</v>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7459,8 +7785,10 @@
           <t>2020-06-06</t>
         </is>
       </c>
-      <c r="E165" t="n">
-        <v>5</v>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7502,8 +7830,10 @@
           <t>2020-09-19</t>
         </is>
       </c>
-      <c r="E166" t="n">
-        <v>5</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7545,8 +7875,10 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v>4</v>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7588,8 +7920,10 @@
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v>4</v>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7631,8 +7965,10 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="E169" t="n">
-        <v>5</v>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7674,8 +8010,10 @@
           <t>2020-10-13</t>
         </is>
       </c>
-      <c r="E170" t="n">
-        <v>5</v>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7717,8 +8055,10 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="E171" t="n">
-        <v>5</v>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7760,8 +8100,10 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>3</v>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7803,8 +8145,10 @@
           <t>2021-12-17</t>
         </is>
       </c>
-      <c r="E173" t="n">
-        <v>4</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>

--- a/profiles.xlsx
+++ b/profiles.xlsx
@@ -10315,19 +10315,23 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AM230123FVVS</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
+          <t>PS060722FVVS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:14:27</t>
+        </is>
+      </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ANJANA DEVI</t>
+          <t>Pujya Shree</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10337,7 +10341,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>3 years 1 months 14 days</t>
+          <t>3 years 8 months 3 days</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10347,7 +10351,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+          <t>Vedic Vidyalayam High School</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10361,39 +10365,43 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AP050222MVVS</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr"/>
+          <t>AM230123FVVS</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:10:10</t>
+        </is>
+      </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Adwith Yadav</t>
+          <t>ANJANA DEVI</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>4 years 1 months 4 days</t>
+          <t>3 years 1 months 14 days</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Vedic Vidyalayam High School</t>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10407,23 +10415,35 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BK120121MATN</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
+          <t>JD310521MVVS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:03:44</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Baladithya</t>
+          <t>JASHWANTH</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>4 years 9 months 6 days</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10431,33 +10451,49 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Amaravathi Talent School</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CC100122MSSA</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+          <t>AP050222MVVS</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:00:28</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Charan</t>
+          <t>Adwith Yadav</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>4 years 1 months 4 days</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10465,39 +10501,47 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
+          <t>Vedic Vidyalayam High School</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GM160722MVVS</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
+          <t>SM210820MVVS</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:57:27</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ganadeep</t>
+          <t>SHIVANSH</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>3 years 7 months 21 days</t>
+          <t>5 years 6 months 16 days</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -10507,7 +10551,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Vedic Vidyalayam High School</t>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10521,29 +10565,33 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>JD310521MVVS</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>PJ290822MVVS</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:54:01</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>JASHWANTH</t>
+          <t>Puneet</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>4 years 9 months 6 days</t>
+          <t>3 years 6 months 8 days</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -10553,7 +10601,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+          <t>Vedic Vidyalayam High School</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10567,34 +10615,38 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MP100821FVVS</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
+          <t>GM160722MVVS</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:50:55</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MedhaSree</t>
+          <t>Ganadeep</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>4 years 6 months 27 days</t>
+          <t>3 years 7 months 21 days</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -10613,19 +10665,23 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PJ290822MVVS</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
+          <t>RM290322FVVS</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:46:37</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Puneet</t>
+          <t>Rajasvi</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-03-29</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10635,12 +10691,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>3 years 6 months 8 days</t>
+          <t>3 years 11 months 8 days</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -10659,29 +10715,33 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS060722FVVS</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
+          <t>SM130122FVVS</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:40:20</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Pujya Shree</t>
+          <t>SATHWIKA</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>3 years 8 months 3 days</t>
+          <t>4 years 1 months 24 days</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -10691,7 +10751,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Vedic Vidyalayam High School</t>
+          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10705,29 +10765,33 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RM290322FVVS</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
+          <t>SS121120FVVS</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:36:10</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Rajasvi</t>
+          <t>SHANMUKHA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>3 years 11 months 8 days</t>
+          <t>5 years 3 months 25 days</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10737,7 +10801,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Vedic Vidyalayam High School</t>
+          <t>VEDIC VIDYALAYAM HUGH SCHOOL</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10751,19 +10815,23 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SM130122FVVS</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
+          <t>MP100821FVVS</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:29:03</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SATHWIKA</t>
+          <t>MedhaSree</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -10773,7 +10841,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>4 years 1 months 24 days</t>
+          <t>4 years 6 months 27 days</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10783,7 +10851,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
+          <t>Vedic Vidyalayam High School</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10797,31 +10865,23 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SM210820MVVS</t>
+          <t>BK120121MATN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SHIVANSH</t>
+          <t>Baladithya</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>5 years 6 months 16 days</t>
-        </is>
-      </c>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10829,60 +10889,44 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>VEDIC VIDYALAYAM HIGH SCHOOL</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
+          <t>Amaravathi Talent School</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SS121120FVVS</t>
+          <t>CC100122MSSA</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SHANMUKHA</t>
+          <t>Charan</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>5 years 3 months 25 days</t>
-        </is>
-      </c>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>VEDIC VIDYALAYAM HUGH SCHOOL</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
+          <t>SHIRDI SAI BABA HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
     </row>
